--- a/docs/downloads/04/tbl_other_act_sex_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_marovoay_bepako.xlsx
@@ -512,12 +512,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -788,12 +782,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-      <c r="E19">
-        <v>0.2</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -903,12 +891,6 @@
           <t>Commerçant</t>
         </is>
       </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-      <c r="E24">
-        <v>0.4</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -972,12 +954,6 @@
           <t>Pêcheur exploitant</t>
         </is>
       </c>
-      <c r="D27">
-        <v>4</v>
-      </c>
-      <c r="E27">
-        <v>0.5</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -994,12 +970,6 @@
         <is>
           <t>Éleveur</t>
         </is>
-      </c>
-      <c r="D28">
-        <v>2</v>
-      </c>
-      <c r="E28">
-        <v>0.3</v>
       </c>
     </row>
     <row r="29">

--- a/docs/downloads/04/tbl_other_act_sex_marovoay_bepako.xlsx
+++ b/docs/downloads/04/tbl_other_act_sex_marovoay_bepako.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -394,14 +394,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D2">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>51.4</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="3">
@@ -417,14 +417,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>66</v>
       </c>
       <c r="E3">
-        <v>4.3</v>
+        <v>48.9</v>
       </c>
     </row>
     <row r="4">
@@ -440,14 +440,8 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>3.1</v>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -463,14 +457,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D5">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="E5">
-        <v>25.7</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="6">
@@ -493,7 +487,7 @@
         <v>27</v>
       </c>
       <c r="E6">
-        <v>10.5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -509,8 +503,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>13</v>
+      </c>
+      <c r="E7">
+        <v>9.6</v>
       </c>
     </row>
     <row r="8">
@@ -521,19 +521,13 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>4.7</v>
+          <t>Artisanat, BTP &amp; Transport</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -549,14 +543,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D9">
-        <v>109</v>
+        <v>20</v>
       </c>
       <c r="E9">
-        <v>70.8</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="10">
@@ -572,14 +566,14 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10">
-        <v>3.9</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="11">
@@ -595,14 +589,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D11">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E11">
-        <v>13</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="12">
@@ -618,37 +612,37 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12">
-        <v>6.5</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Marovoay - Tous</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Homme</t>
+          <t>Femme</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Étudiant</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D13">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E13">
-        <v>5.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -664,14 +658,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Commerce &amp; Restauration</t>
         </is>
       </c>
       <c r="D14">
-        <v>505</v>
+        <v>60</v>
       </c>
       <c r="E14">
-        <v>48.3</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="15">
@@ -687,14 +681,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D15">
-        <v>44</v>
+        <v>317</v>
       </c>
       <c r="E15">
-        <v>4.2</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="16">
@@ -710,14 +704,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Commerçant</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D16">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="E16">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="17">
@@ -733,14 +727,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Elève / Etudiant</t>
         </is>
       </c>
       <c r="D17">
-        <v>317</v>
+        <v>34</v>
       </c>
       <c r="E17">
-        <v>30.3</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="18">
@@ -763,7 +757,7 @@
         <v>99</v>
       </c>
       <c r="E18">
-        <v>9.5</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="19">
@@ -779,8 +773,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pêcheur exploitant</t>
-        </is>
+          <t>Services &amp; Autres</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>57</v>
+      </c>
+      <c r="E19">
+        <v>9.6</v>
       </c>
     </row>
     <row r="20">
@@ -791,19 +791,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Éleveur</t>
+          <t>Artisanat, BTP &amp; Transport</t>
         </is>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="E20">
-        <v>0.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="21">
@@ -814,19 +814,13 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Femme</t>
+          <t>Homme</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D21">
-        <v>34</v>
-      </c>
-      <c r="E21">
-        <v>3.3</v>
+          <t>Commerce &amp; Restauration</t>
+        </is>
       </c>
     </row>
     <row r="22">
@@ -842,14 +836,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Autres</t>
+          <t>Cultivateur exploitant</t>
         </is>
       </c>
       <c r="D22">
-        <v>496</v>
+        <v>101</v>
       </c>
       <c r="E22">
-        <v>67.90000000000001</v>
+        <v>39.1</v>
       </c>
     </row>
     <row r="23">
@@ -865,14 +859,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Chômeur</t>
+          <t>Elevage, Pêche &amp; Ress. nat.</t>
         </is>
       </c>
       <c r="D23">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="E23">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="24">
@@ -888,8 +882,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Commerçant</t>
-        </is>
+          <t>Elève / Etudiant</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>46</v>
+      </c>
+      <c r="E24">
+        <v>17.8</v>
       </c>
     </row>
     <row r="25">
@@ -905,14 +905,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cultivateur</t>
+          <t>Ouvrier agricole</t>
         </is>
       </c>
       <c r="D25">
-        <v>101</v>
+        <v>48</v>
       </c>
       <c r="E25">
-        <v>13.8</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="26">
@@ -928,71 +928,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Ouvrier agricole</t>
+          <t>Services &amp; Autres</t>
         </is>
       </c>
       <c r="D26">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="E26">
-        <v>6.6</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Pêcheur exploitant</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Éleveur</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Marovoay - Tous</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Homme</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Étudiant</t>
-        </is>
-      </c>
-      <c r="D29">
-        <v>46</v>
-      </c>
-      <c r="E29">
-        <v>6.3</v>
+        <v>14.3</v>
       </c>
     </row>
   </sheetData>
